--- a/이슈관리_기타_제조사업부_아모레_0902.xlsx
+++ b/이슈관리_기타_제조사업부_아모레_0902.xlsx
@@ -119,7 +119,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -238,11 +238,151 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="009DB2CE"/>
+      </left>
+      <right style="thin">
+        <color rgb="009DB2CE"/>
+      </right>
+      <top style="medium">
+        <color rgb="001F3864"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009DB2CE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="009DB2CE"/>
+      </left>
+      <right style="thin">
+        <color rgb="009DB2CE"/>
+      </right>
+      <top style="thin">
+        <color rgb="009DB2CE"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001F3864"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001F3864"/>
+      </left>
+      <right style="thin">
+        <color rgb="009DB2CE"/>
+      </right>
+      <top style="medium">
+        <color rgb="001F3864"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009DB2CE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="009DB2CE"/>
+      </left>
+      <right style="medium">
+        <color rgb="001F3864"/>
+      </right>
+      <top style="medium">
+        <color rgb="001F3864"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009DB2CE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001F3864"/>
+      </left>
+      <right style="thin">
+        <color rgb="009DB2CE"/>
+      </right>
+      <top style="thin">
+        <color rgb="009DB2CE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009DB2CE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="009DB2CE"/>
+      </left>
+      <right style="medium">
+        <color rgb="001F3864"/>
+      </right>
+      <top style="thin">
+        <color rgb="009DB2CE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009DB2CE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001F3864"/>
+      </left>
+      <right style="thin">
+        <color rgb="009DB2CE"/>
+      </right>
+      <top style="thin">
+        <color rgb="009DB2CE"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001F3864"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="009DB2CE"/>
+      </left>
+      <right style="medium">
+        <color rgb="001F3864"/>
+      </right>
+      <top style="thin">
+        <color rgb="009DB2CE"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001F3864"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001F3864"/>
+      </left>
+      <right style="medium">
+        <color rgb="001F3864"/>
+      </right>
+      <top style="medium">
+        <color rgb="001F3864"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009DB2CE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001F3864"/>
+      </left>
+      <right style="medium">
+        <color rgb="001F3864"/>
+      </right>
+      <top style="thin">
+        <color rgb="009DB2CE"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001F3864"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -252,53 +392,85 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -714,23 +886,23 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>사업부</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>거래처명</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>이슈</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>필요조치</t>
         </is>
@@ -740,565 +912,565 @@
           <t>진행사항</t>
         </is>
       </c>
-      <c r="H3" s="6" t="n"/>
+      <c r="H3" s="7" t="n"/>
       <c r="I3" s="5" t="inlineStr">
         <is>
           <t>기한</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>진도</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="6" t="n"/>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="11" t="n"/>
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="13" t="n"/>
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="13" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>제조</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>아모레퍼시픽</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n"/>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="D5" s="18" t="n"/>
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>고용노동부 캠페인 활동 및 현장 점검</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>• 캠페인 운영 및 현장 대응 준비
 • 점검 대상 사업장 사전 확인, 정비</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>금주</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="22" t="inlineStr">
         <is>
           <t>• 8/28 방문 현장 동선 수립 및 현장 점검 완료
 • 8/31 캠페인 운영 및 현장 순회 점검 완료
 • 점검 지적사항 정리 및 시정 착수  ※ 결과 반영 필요</t>
         </is>
       </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="I5" s="23" t="inlineStr">
         <is>
           <t>9/5</t>
         </is>
       </c>
-      <c r="J5" s="15" t="inlineStr">
+      <c r="J5" s="24" t="inlineStr">
         <is>
           <t>진행</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="16" t="n"/>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="A6" s="25" t="n"/>
+      <c r="B6" s="26" t="n"/>
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>이민아</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>기존</t>
         </is>
       </c>
-      <c r="E6" s="19" t="n"/>
-      <c r="F6" s="19" t="n"/>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="E6" s="29" t="n"/>
+      <c r="F6" s="29" t="n"/>
+      <c r="G6" s="30" t="inlineStr">
         <is>
           <t>차주</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="31" t="inlineStr">
         <is>
           <t>• 시정 결과 회신 및 재발 방지 표준화
 • 근로시간 관리 실태 자체 점검 병행 (아래 4번 연계)</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="32" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr">
+      <c r="J6" s="33" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>제조</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>아모레퍼시픽</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n"/>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="D7" s="18" t="n"/>
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>38주 물량 Gap 대응 및 충원 규모 협의
 — Gap 292,964 EA / 충원 기준 상이 (제니엘 12명 ↔ AP 6명)</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>• AP 대응전략 검토 의견 회신
 • 충원 규모 재합의 근거 확보
 • 세정·멀티 증설안 산식 검증</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>금주</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="34" t="inlineStr">
         <is>
           <t>• 9/2 38주 대응전략 검토 회신 제출 (항목별 가능/조건부/재검토 판정)
 • AP 제공 라인별 표준 소요 분석 → OP 부족 13명 확인, AP 최대안(13명)과 일치
 • 원청 인력의 도급 라인 상주는 위장도급 소지로 재검토 요청</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>9/2</t>
         </is>
       </c>
-      <c r="J7" s="15" t="inlineStr">
+      <c r="J7" s="24" t="inlineStr">
         <is>
           <t>진행</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="16" t="n"/>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="A8" s="25" t="n"/>
+      <c r="B8" s="26" t="n"/>
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>이민아</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="35" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="E8" s="19" t="n"/>
-      <c r="F8" s="19" t="n"/>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="29" t="n"/>
+      <c r="G8" s="30" t="inlineStr">
         <is>
           <t>차주</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="31" t="inlineStr">
         <is>
           <t>• 충원 13명 기준으로 재협의 (6명은 AP 최소안 = Gap 47,272 EA 미달)
 • 멀티 분당 CAPA 확정 (AP 32 ↔ 원본 35, 2안 +9,900 EA 차이)</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="I8" s="32" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="J8" s="20" t="inlineStr">
+      <c r="J8" s="33" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>제조</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>아모레퍼시픽</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>비정규 인력 구분 및 OP 육성·충원 월별 계획
 — AP 요구 3건 (9/1 기한)</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>• 일용 / 일용외 구분표 제출
 • OP 육성·충원·전환 월별 계획
 • 단기 대응 인원수 확정</t>
         </is>
       </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>금주</t>
         </is>
       </c>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="H9" s="36" t="inlineStr">
         <is>
           <t>• 9/1 1장 자료 제출 완료
 • 제출본 수치 불일치 확인 — 충원 6/3/7명, 교육 8/5/10명 혼재 → 정정본 작성 중
 • 작업자(비 OP) 부족 63명 산출 (HnB 31 · 염모 22 · 치약 10)</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="I9" s="23" t="inlineStr">
         <is>
           <t>9/5</t>
         </is>
       </c>
-      <c r="J9" s="15" t="inlineStr">
+      <c r="J9" s="24" t="inlineStr">
         <is>
           <t>진행</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="16" t="n"/>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="A10" s="25" t="n"/>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>이민아</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="35" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="E10" s="19" t="n"/>
-      <c r="F10" s="19" t="n"/>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="E10" s="29" t="n"/>
+      <c r="F10" s="29" t="n"/>
+      <c r="G10" s="30" t="inlineStr">
         <is>
           <t>차주</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="H10" s="31" t="inlineStr">
         <is>
           <t>• 정정본 재제출 및 기초·기말 인원 연쇄 정합
 • 일용 확보 경로 / 단가 확정</t>
         </is>
       </c>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="I10" s="32" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="J10" s="20" t="inlineStr">
+      <c r="J10" s="33" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>제조</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>아모레퍼시픽</t>
         </is>
       </c>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>주 52시간 · 3개월 탄력근로 한도 관리
 — 현 단위기간 7·8·9월 (한도 156H)</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>• 9월 초과 예상 인원 편성 축소
 • 8월 시간외 구성 소명자료 정비
 • 10~12월 단위기간 서면합의 (10/1 전)</t>
         </is>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>금주</t>
         </is>
       </c>
-      <c r="H11" s="23" t="inlineStr">
+      <c r="H11" s="36" t="inlineStr">
         <is>
           <t>• 9월을 8월 수준 풀 특근 시 38명이 156H 초과 — 전사 1,438H(21%) 편성 불가
 • 8월 개인 최대 108.5H = 주 25H 환산으로 주 12H 한도 초과 소지 → 고용노동부 점검 리스크
 • 잔여 0H 4명 9월 시간외 전면 제외 / 세척실·주임·HnB는 재배분 불가 확인</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="23" t="inlineStr">
         <is>
           <t>9/6</t>
         </is>
       </c>
-      <c r="J11" s="15" t="inlineStr">
+      <c r="J11" s="24" t="inlineStr">
         <is>
           <t>진행</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="16" t="n"/>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="A12" s="25" t="n"/>
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>이민아</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="35" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="13" t="inlineStr">
+      <c r="E12" s="29" t="n"/>
+      <c r="F12" s="29" t="n"/>
+      <c r="G12" s="30" t="inlineStr">
         <is>
           <t>차주</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="37" t="inlineStr">
         <is>
           <t>• 근로자대표 서면합의 초안 및 10~12월 근무표 작성 (10/1 전 체결 필수)
 • 세척실·주임·HnB 대체 편성안 확정</t>
         </is>
       </c>
-      <c r="I12" s="14" t="inlineStr">
+      <c r="I12" s="32" t="inlineStr">
         <is>
           <t>9/30</t>
         </is>
       </c>
-      <c r="J12" s="20" t="inlineStr">
+      <c r="J12" s="33" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>제조</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>아모레퍼시픽</t>
         </is>
       </c>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="19" t="inlineStr">
         <is>
           <t>10월 특근 편성 ↔ MES 확보 일정 상충
 — AP 요구 '주 12H 연장 + 특근 8H'</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>• 주 20H 편성 불가 사유 회신
 • MES 확보 3안(9/23) 확정 요청
 • 10~12월 확정 오더 수령</t>
         </is>
       </c>
-      <c r="G13" s="13" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>금주</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="34" t="inlineStr">
         <is>
           <t>• '평일 12H + 특근 8H = 주 20H'는 근기법 §53 위반 (휴일근로 포함 한도) → 회신
 • 대안 3안 제시 : ①220H 즉시 / ③236H 토 2회 소정화 / ④256H 토 5회 소정화
 • 10월 1·2주 연속 특근은 MES 1안(10/3)·2안(10/10)과 양립 불가 — 3안만 가능</t>
         </is>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t>9/2</t>
         </is>
       </c>
-      <c r="J13" s="15" t="inlineStr">
+      <c r="J13" s="24" t="inlineStr">
         <is>
           <t>진행</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="16" t="n"/>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="A14" s="25" t="n"/>
+      <c r="B14" s="26" t="n"/>
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>이민아</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="35" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="E14" s="19" t="n"/>
-      <c r="F14" s="19" t="n"/>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="E14" s="29" t="n"/>
+      <c r="F14" s="29" t="n"/>
+      <c r="G14" s="30" t="inlineStr">
         <is>
           <t>차주</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr">
+      <c r="H14" s="31" t="inlineStr">
         <is>
           <t>• 확정 오더 수령 후 ①/③/④ 중 편성안 확정
 • 10/3·10/5·10/9 유급휴일 근로 가산 및 여성 근로자 개별 동의 절차</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="32" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="J14" s="20" t="inlineStr">
+      <c r="J14" s="33" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>제조</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>아모레퍼시픽</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="19" t="inlineStr">
         <is>
           <t>튜브 라인 계획-실적 GAP 및 LOSS 귀책
 — 8/27 AP 생산지원팀 제기</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>• 일별 계획-실적 대조 및 귀책 3분류
 • UPH 실측 반영 후 LOSS 재산정
 • 포장재 결품 이력 정리</t>
         </is>
       </c>
-      <c r="G15" s="13" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>금주</t>
         </is>
       </c>
-      <c r="H15" s="12" t="inlineStr">
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>• 대조·LOSS 산정 워크북 작성 (원청/도급/공통 귀책 분리)
 • 튜브 실제 CAPA 45~54개/분(2,700~3,240개/H) 확인 → 기존 350개/H 가정 폐기
 • 라인 표준상 튜브 OP 부족 0명 — 인원이 아닌 가동대수·잔업 편성 문제로 확인</t>
         </is>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>9/6</t>
         </is>
       </c>
-      <c r="J15" s="15" t="inlineStr">
+      <c r="J15" s="24" t="inlineStr">
         <is>
           <t>진행</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="16" t="n"/>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="A16" s="25" t="n"/>
+      <c r="B16" s="26" t="n"/>
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>이민아</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="35" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="E16" s="19" t="n"/>
-      <c r="F16" s="19" t="n"/>
-      <c r="G16" s="13" t="inlineStr">
+      <c r="E16" s="29" t="n"/>
+      <c r="F16" s="29" t="n"/>
+      <c r="G16" s="30" t="inlineStr">
         <is>
           <t>차주</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
+      <c r="H16" s="31" t="inlineStr">
         <is>
           <t>• 실측 UPH 반영 LOSS 금액 재산출 및 귀책 협의
 • 9호기(초음파) 미가동 사유 및 재가동 계획 확인</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="I16" s="32" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
-      <c r="J16" s="20" t="inlineStr">
+      <c r="J16" s="33" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="n"/>
+      <c r="A17" s="38" t="n"/>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>※ 회색 강조 = 법적 리스크 항목.  4번(주 52시간)과 1번(고용노동부 점검)은 직접 연결됨 — 점검 시 8월 시간외 실적(개인 최대 108.5H)의 구성 소명이 필요하다.  1번 금주 진행사항의 점검 결과는 실제 내용으로 교체 요망.  |  작성 2026.09.02</t>
         </is>

--- a/이슈관리_기타_제조사업부_아모레_0902.xlsx
+++ b/이슈관리_기타_제조사업부_아모레_0902.xlsx
@@ -10,7 +10,7 @@
     <sheet name="이슈관리_기타" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'이슈관리_기타'!$A$1:$J$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'이슈관리_기타'!$A$1:$J$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -73,7 +73,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -113,11 +113,6 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4E4"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="21">
     <border>
@@ -382,7 +377,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -466,12 +461,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -844,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.5" customWidth="1" min="1" max="1"/>
@@ -975,7 +964,7 @@
         <is>
           <t>• 8/28 방문 현장 동선 수립 및 현장 점검 완료
 • 8/31 캠페인 운영 및 현장 순회 점검 완료
-• 점검 지적사항 정리 및 시정 착수  ※ 결과 반영 필요</t>
+• 점검 지적사항 정리 및 시정 착수   ※ 실제 결과로 교체 요망</t>
         </is>
       </c>
       <c r="I5" s="23" t="inlineStr">
@@ -1012,7 +1001,7 @@
       <c r="H6" s="31" t="inlineStr">
         <is>
           <t>• 시정 결과 회신 및 재발 방지 표준화
-• 근로시간 관리 실태 자체 점검 병행 (아래 4번 연계)</t>
+• 근로시간 관리 실태 자체 점검 병행 (2번 연계)</t>
         </is>
       </c>
       <c r="I6" s="32" t="inlineStr">
@@ -1026,7 +1015,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="26" customHeight="1">
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="15" t="n">
         <v>2</v>
       </c>
@@ -1043,15 +1032,19 @@
       <c r="D7" s="18" t="n"/>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t>38주 물량 Gap 대응 및 충원 규모 협의
-— Gap 292,964 EA / 충원 기준 상이 (제니엘 12명 ↔ AP 6명)</t>
+          <t>아모레퍼시픽 물량 증가 대응 (38주 ~)
+• 물량 Gap 292,964 EA
+• 라인 표준 OP 부족 13명
+• 3개월 탄력근로 한도(156H) 소진 임박</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>• AP 대응전략 검토 의견 회신
-• 충원 규모 재합의 근거 확보
-• 세정·멀티 증설안 산식 검증</t>
+          <t>① 충원 규모 재합의
+    (제니엘 13명 ↔ AP 6명)
+② 증산 라인 편성 및 소요 인원 확보
+③ 주 52시간 한도 내 특근 편성
+④ 10월 특근 ↔ MES 확보 일정 조율</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -1061,9 +1054,11 @@
       </c>
       <c r="H7" s="34" t="inlineStr">
         <is>
-          <t>• 9/2 38주 대응전략 검토 회신 제출 (항목별 가능/조건부/재검토 판정)
-• AP 제공 라인별 표준 소요 분석 → OP 부족 13명 확인, AP 최대안(13명)과 일치
-• 원청 인력의 도급 라인 상주는 위장도급 소지로 재검토 요청</t>
+          <t>• 9/2 38주 대응전략 검토 회신 제출 — 세정·멀티 증설 조건부 가능, 원청 인력의 도급 라인 상주는 위장도급 소지로 재검토 요청
+• AP 제공 라인별 표준 소요 분석 → OP 부족 13명 (AP 최대안과 일치). 충원 6명은 AP 최소안으로 Gap 47,272 EA 미달 / 작업자(비 OP)는 별도 63명 부족
+• 9월을 8월 수준 풀 특근 시 38명이 3개월 한도 156H 초과 — 전사 1,438H(21%) 편성 불가. 세척실·주임·HnB는 공정 내 재배분 불가로 충원이 전제
+• AP 요구 '평일 연장 12H + 특근 8H = 주 20H'는 근기법 §53 위반 → 적법 대안 3안 회신 (①220H 즉시 / ③236H 토 2회 소정화 / ④256H 토 5회 소정화)
+• 튜브 실측 CAPA 45~54개/분 확인 — 튜브 OP 부족 0명으로 인원이 아닌 가동대수·잔업 편성 문제</t>
         </is>
       </c>
       <c r="I7" s="23" t="inlineStr">
@@ -1077,7 +1072,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="26" customHeight="1">
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="25" t="n"/>
       <c r="B8" s="26" t="n"/>
       <c r="C8" s="27" t="inlineStr">
@@ -1099,8 +1094,11 @@
       </c>
       <c r="H8" s="31" t="inlineStr">
         <is>
-          <t>• 충원 13명 기준으로 재협의 (6명은 AP 최소안 = Gap 47,272 EA 미달)
-• 멀티 분당 CAPA 확정 (AP 32 ↔ 원본 35, 2안 +9,900 EA 차이)</t>
+          <t>• 충원 13명 기준 재협의 및 일용 / 일용외 확보 경로·단가 확정
+• 10~12월 확정 오더 수령 후 편성안(①/③/④) 확정
+• 10·11·12월 단위기간 근로자대표 서면합의 및 근무표 작성 — 10/1 전 체결 필수
+• MES 확보 3안(9/23) 확정 요청 — 1안(10/3)·2안(10/10)은 10월 1·2주 연속 특근과 양립 불가
+• 세척실·주임·HnB 대체 편성안 확정 / 튜브 실측 UPH 반영 LOSS 재산출</t>
         </is>
       </c>
       <c r="I8" s="32" t="inlineStr">
@@ -1114,411 +1112,39 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>제조</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>아모레퍼시픽</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="n"/>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>비정규 인력 구분 및 OP 육성·충원 월별 계획
-— AP 요구 3건 (9/1 기한)</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>• 일용 / 일용외 구분표 제출
-• OP 육성·충원·전환 월별 계획
-• 단기 대응 인원수 확정</t>
-        </is>
-      </c>
-      <c r="G9" s="21" t="inlineStr">
-        <is>
-          <t>금주</t>
-        </is>
-      </c>
-      <c r="H9" s="36" t="inlineStr">
-        <is>
-          <t>• 9/1 1장 자료 제출 완료
-• 제출본 수치 불일치 확인 — 충원 6/3/7명, 교육 8/5/10명 혼재 → 정정본 작성 중
-• 작업자(비 OP) 부족 63명 산출 (HnB 31 · 염모 22 · 치약 10)</t>
-        </is>
-      </c>
-      <c r="I9" s="23" t="inlineStr">
-        <is>
-          <t>9/5</t>
-        </is>
-      </c>
-      <c r="J9" s="24" t="inlineStr">
-        <is>
-          <t>진행</t>
-        </is>
-      </c>
+    <row r="9">
+      <c r="A9" s="36" t="n"/>
     </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="25" t="n"/>
-      <c r="B10" s="26" t="n"/>
-      <c r="C10" s="27" t="inlineStr">
-        <is>
-          <t>이민아</t>
-        </is>
-      </c>
-      <c r="D10" s="35" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E10" s="29" t="n"/>
-      <c r="F10" s="29" t="n"/>
-      <c r="G10" s="30" t="inlineStr">
-        <is>
-          <t>차주</t>
-        </is>
-      </c>
-      <c r="H10" s="31" t="inlineStr">
-        <is>
-          <t>• 정정본 재제출 및 기초·기말 인원 연쇄 정합
-• 일용 확보 경로 / 단가 확정</t>
-        </is>
-      </c>
-      <c r="I10" s="32" t="inlineStr">
-        <is>
-          <t>9/12</t>
-        </is>
-      </c>
-      <c r="J10" s="33" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>제조</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>아모레퍼시픽</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="n"/>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>주 52시간 · 3개월 탄력근로 한도 관리
-— 현 단위기간 7·8·9월 (한도 156H)</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="inlineStr">
-        <is>
-          <t>• 9월 초과 예상 인원 편성 축소
-• 8월 시간외 구성 소명자료 정비
-• 10~12월 단위기간 서면합의 (10/1 전)</t>
-        </is>
-      </c>
-      <c r="G11" s="21" t="inlineStr">
-        <is>
-          <t>금주</t>
-        </is>
-      </c>
-      <c r="H11" s="36" t="inlineStr">
-        <is>
-          <t>• 9월을 8월 수준 풀 특근 시 38명이 156H 초과 — 전사 1,438H(21%) 편성 불가
-• 8월 개인 최대 108.5H = 주 25H 환산으로 주 12H 한도 초과 소지 → 고용노동부 점검 리스크
-• 잔여 0H 4명 9월 시간외 전면 제외 / 세척실·주임·HnB는 재배분 불가 확인</t>
-        </is>
-      </c>
-      <c r="I11" s="23" t="inlineStr">
-        <is>
-          <t>9/6</t>
-        </is>
-      </c>
-      <c r="J11" s="24" t="inlineStr">
-        <is>
-          <t>진행</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="25" t="n"/>
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="27" t="inlineStr">
-        <is>
-          <t>이민아</t>
-        </is>
-      </c>
-      <c r="D12" s="35" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E12" s="29" t="n"/>
-      <c r="F12" s="29" t="n"/>
-      <c r="G12" s="30" t="inlineStr">
-        <is>
-          <t>차주</t>
-        </is>
-      </c>
-      <c r="H12" s="37" t="inlineStr">
-        <is>
-          <t>• 근로자대표 서면합의 초안 및 10~12월 근무표 작성 (10/1 전 체결 필수)
-• 세척실·주임·HnB 대체 편성안 확정</t>
-        </is>
-      </c>
-      <c r="I12" s="32" t="inlineStr">
-        <is>
-          <t>9/30</t>
-        </is>
-      </c>
-      <c r="J12" s="33" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>제조</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>아모레퍼시픽</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="n"/>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>10월 특근 편성 ↔ MES 확보 일정 상충
-— AP 요구 '주 12H 연장 + 특근 8H'</t>
-        </is>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
-        <is>
-          <t>• 주 20H 편성 불가 사유 회신
-• MES 확보 3안(9/23) 확정 요청
-• 10~12월 확정 오더 수령</t>
-        </is>
-      </c>
-      <c r="G13" s="21" t="inlineStr">
-        <is>
-          <t>금주</t>
-        </is>
-      </c>
-      <c r="H13" s="34" t="inlineStr">
-        <is>
-          <t>• '평일 12H + 특근 8H = 주 20H'는 근기법 §53 위반 (휴일근로 포함 한도) → 회신
-• 대안 3안 제시 : ①220H 즉시 / ③236H 토 2회 소정화 / ④256H 토 5회 소정화
-• 10월 1·2주 연속 특근은 MES 1안(10/3)·2안(10/10)과 양립 불가 — 3안만 가능</t>
-        </is>
-      </c>
-      <c r="I13" s="23" t="inlineStr">
-        <is>
-          <t>9/2</t>
-        </is>
-      </c>
-      <c r="J13" s="24" t="inlineStr">
-        <is>
-          <t>진행</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="25" t="n"/>
-      <c r="B14" s="26" t="n"/>
-      <c r="C14" s="27" t="inlineStr">
-        <is>
-          <t>이민아</t>
-        </is>
-      </c>
-      <c r="D14" s="35" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E14" s="29" t="n"/>
-      <c r="F14" s="29" t="n"/>
-      <c r="G14" s="30" t="inlineStr">
-        <is>
-          <t>차주</t>
-        </is>
-      </c>
-      <c r="H14" s="31" t="inlineStr">
-        <is>
-          <t>• 확정 오더 수령 후 ①/③/④ 중 편성안 확정
-• 10/3·10/5·10/9 유급휴일 근로 가산 및 여성 근로자 개별 동의 절차</t>
-        </is>
-      </c>
-      <c r="I14" s="32" t="inlineStr">
-        <is>
-          <t>9/12</t>
-        </is>
-      </c>
-      <c r="J14" s="33" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>제조</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>아모레퍼시픽</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="n"/>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>튜브 라인 계획-실적 GAP 및 LOSS 귀책
-— 8/27 AP 생산지원팀 제기</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>• 일별 계획-실적 대조 및 귀책 3분류
-• UPH 실측 반영 후 LOSS 재산정
-• 포장재 결품 이력 정리</t>
-        </is>
-      </c>
-      <c r="G15" s="21" t="inlineStr">
-        <is>
-          <t>금주</t>
-        </is>
-      </c>
-      <c r="H15" s="22" t="inlineStr">
-        <is>
-          <t>• 대조·LOSS 산정 워크북 작성 (원청/도급/공통 귀책 분리)
-• 튜브 실제 CAPA 45~54개/분(2,700~3,240개/H) 확인 → 기존 350개/H 가정 폐기
-• 라인 표준상 튜브 OP 부족 0명 — 인원이 아닌 가동대수·잔업 편성 문제로 확인</t>
-        </is>
-      </c>
-      <c r="I15" s="23" t="inlineStr">
-        <is>
-          <t>9/6</t>
-        </is>
-      </c>
-      <c r="J15" s="24" t="inlineStr">
-        <is>
-          <t>진행</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="25" t="n"/>
-      <c r="B16" s="26" t="n"/>
-      <c r="C16" s="27" t="inlineStr">
-        <is>
-          <t>이민아</t>
-        </is>
-      </c>
-      <c r="D16" s="35" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E16" s="29" t="n"/>
-      <c r="F16" s="29" t="n"/>
-      <c r="G16" s="30" t="inlineStr">
-        <is>
-          <t>차주</t>
-        </is>
-      </c>
-      <c r="H16" s="31" t="inlineStr">
-        <is>
-          <t>• 실측 UPH 반영 LOSS 금액 재산출 및 귀책 협의
-• 9호기(초음파) 미가동 사유 및 재가동 계획 확인</t>
-        </is>
-      </c>
-      <c r="I16" s="32" t="inlineStr">
-        <is>
-          <t>9/12</t>
-        </is>
-      </c>
-      <c r="J16" s="33" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="38" t="n"/>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="39" t="inlineStr">
-        <is>
-          <t>※ 회색 강조 = 법적 리스크 항목.  4번(주 52시간)과 1번(고용노동부 점검)은 직접 연결됨 — 점검 시 8월 시간외 실적(개인 최대 108.5H)의 구성 소명이 필요하다.  1번 금주 진행사항의 점검 결과는 실제 내용으로 교체 요망.  |  작성 2026.09.02</t>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>※ 1번(고용노동부 점검)과 2번(물량 증가 대응)은 직접 연결됨 — 점검 시 8월 시간외 실적(개인 최대 108.5H = 주 25H 환산)의 구성 소명이 필요하다.  1번 금주 진행사항은 실제 점검 결과로 교체 요망.  |  작성 2026.09.02</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="42">
-    <mergeCell ref="F15:F16"/>
+  <mergeCells count="22">
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="C15:D15"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="E13:E14"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B11:B12"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A10:J10"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="B13:B14"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="I3:I4"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B15:B16"/>
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="C11:D11"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F11:F12"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A18:J18"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="A15:A16"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C13:D13"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="C3:D3"/>
-    <mergeCell ref="A11:A12"/>
     <mergeCell ref="G3:H4"/>
   </mergeCells>
   <pageMargins left="0.2" right="0.2" top="0.25" bottom="0.25" header="0.5" footer="0.5"/>
